--- a/Weekly_Paid_Payments_Krishi_Bills_OCtober_2026/Purchase_list_Account Transfer from company_Date_From 10-10-2026 to 16-10-2026/Weekly_Payments Details _From_Date_10-10-2026_to_16-10-2026.pdf.xlsx
+++ b/Weekly_Paid_Payments_Krishi_Bills_OCtober_2026/Purchase_list_Account Transfer from company_Date_From 10-10-2026 to 16-10-2026/Weekly_Payments Details _From_Date_10-10-2026_to_16-10-2026.pdf.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\Weekly_Paid_Payments_Krishi_Bills_OCtober_2026\Purchase_list_Account Transfer from company_Date_From 10-10-2026 to 16-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{521DCAA3-3C03-4084-AFC8-670A9D851139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F501E2F-BCE5-4A31-B386-70474E5BEB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{AFD74B07-5F1A-49C1-8FFF-FFA9C3790DE7}"/>
   </bookViews>
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -259,6 +259,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -755,7 +758,7 @@
       <c r="D10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="14">
         <v>27018</v>
       </c>
       <c r="F10" s="10" t="s">
@@ -775,7 +778,7 @@
       <c r="D11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="14">
         <v>12390</v>
       </c>
       <c r="F11" s="10" t="s">
@@ -795,7 +798,7 @@
       <c r="D12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="14">
         <v>12006</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -815,7 +818,7 @@
       <c r="D13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="14">
         <v>2000</v>
       </c>
       <c r="F13" s="7" t="s">
